--- a/data/trans_orig/P64D$andando_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P64D$andando_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según cómo se desplaza desde su casa al centro de trabajo/estudios, mediante, al menos, una de las opciones (multirrespuesta) en 2023</t>
+          <t>Población según cómo se desplaza desde su casa al centro de trabajo/estudios, mediante, al menos, una de las opciones (multirrespuesta) en 2023 (tasa de respuesta: 99,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12713</t>
+          <t>11953</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29898</t>
+          <t>30748</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>33537</t>
+          <t>34136</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>51080</t>
+          <t>52604</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>41,69%</t>
+          <t>42,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>63,5%</t>
+          <t>65,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>48927</t>
+          <t>48890</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>77462</t>
+          <t>78031</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,44%</t>
+          <t>36,71%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>316</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5885</t>
+          <t>6313</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>333</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5950</t>
+          <t>7124</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,35%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>98111</t>
+          <t>97527</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>116457</t>
+          <t>116942</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>74,27%</t>
+          <t>73,83%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>88,52%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>22815</t>
+          <t>21544</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>39949</t>
+          <t>38740</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>49,66%</t>
+          <t>48,16%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>125050</t>
+          <t>123510</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>153972</t>
+          <t>152505</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>58,83%</t>
+          <t>58,11%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>72,44%</t>
+          <t>71,75%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2620</t>
+          <t>2691</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12234</t>
+          <t>12271</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10547</t>
+          <t>10294</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32650</t>
+          <t>32330</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,59%</t>
+          <t>40,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14538</t>
+          <t>13999</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>39572</t>
+          <t>41845</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>19,69%</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5849</t>
+          <t>6229</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,62 +1217,62 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>1319</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>1264</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>6271</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,62%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>1,57%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1319</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>5365</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>886</t>
+          <t>773</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9638</t>
+          <t>9950</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1330,12 +1330,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>1452</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6620</t>
+          <t>7321</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1345,12 +1345,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1365,12 +1365,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3363</t>
+          <t>3333</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>13105</t>
+          <t>13330</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1380,12 +1380,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>131373</t>
+          <t>132508</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>314824</t>
+          <t>312683</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>233407</t>
+          <t>240180</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>351504</t>
+          <t>353554</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>37,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>395133</t>
+          <t>384732</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>651562</t>
+          <t>647313</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>27,81%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6698</t>
+          <t>6396</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27627</t>
+          <t>27812</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3385</t>
+          <t>3534</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>274404</t>
+          <t>280571</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>15981</t>
+          <t>16015</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>324989</t>
+          <t>349697</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>15,03%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1053040</t>
+          <t>1050924</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1238822</t>
+          <t>1242083</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>76,18%</t>
+          <t>76,02%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>89,85%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>430456</t>
+          <t>422234</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>611084</t>
+          <t>613816</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>44,68%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>64,67%</t>
+          <t>64,96%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1522400</t>
+          <t>1530667</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1840389</t>
+          <t>1859802</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>65,41%</t>
+          <t>65,77%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>79,08%</t>
+          <t>79,91%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>51315</t>
+          <t>49529</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>122069</t>
+          <t>121500</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>71971</t>
+          <t>71880</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>116922</t>
+          <t>118154</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>131448</t>
+          <t>130426</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>225102</t>
+          <t>222651</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,57%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4733</t>
+          <t>5081</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21410</t>
+          <t>21558</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1814</t>
+          <t>1877</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>10899</t>
+          <t>10043</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8765</t>
+          <t>8471</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>25866</t>
+          <t>26363</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
@@ -1977,12 +1977,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14564</t>
+          <t>13982</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>46252</t>
+          <t>46913</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1992,12 +1992,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2012,12 +2012,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>17250</t>
+          <t>17591</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>36206</t>
+          <t>37144</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>36435</t>
+          <t>34662</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>74489</t>
+          <t>74706</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>97236</t>
+          <t>95323</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>136036</t>
+          <t>136533</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>128379</t>
+          <t>128708</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>164529</t>
+          <t>162735</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>37,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>232712</t>
+          <t>234972</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>283710</t>
+          <t>284806</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>32,27%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4168</t>
+          <t>4195</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15456</t>
+          <t>16126</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2097</t>
+          <t>2404</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10298</t>
+          <t>10286</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>8331</t>
+          <t>8562</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>23151</t>
+          <t>22011</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>276970</t>
+          <t>278834</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>319954</t>
+          <t>323532</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,49 +2335,49 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>61,92%</t>
+          <t>62,34%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
+          <t>72,33%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>294429</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>276325</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>311402</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>67,63%</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>63,47%</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
           <t>71,53%</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>433</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>294429</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>277758</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>311005</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>67,63%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>63,8%</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>71,44%</t>
-        </is>
-      </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
           <t>720</t>
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>565724</t>
+          <t>565212</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>619556</t>
+          <t>622478</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>64,09%</t>
+          <t>64,04%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>70,19%</t>
+          <t>70,52%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>18891</t>
+          <t>18690</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>40263</t>
+          <t>41834</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>28325</t>
+          <t>27118</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>48331</t>
+          <t>48443</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>52284</t>
+          <t>51019</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>82528</t>
+          <t>81410</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,22%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1383</t>
+          <t>1360</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>11279</t>
+          <t>10981</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1305</t>
+          <t>1283</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11121</t>
+          <t>10560</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3440</t>
+          <t>3453</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>17709</t>
+          <t>17628</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -2659,12 +2659,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>27234</t>
+          <t>28985</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>57233</t>
+          <t>57249</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>15824</t>
+          <t>15878</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>32652</t>
+          <t>33010</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2709,12 +2709,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>49197</t>
+          <t>50803</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>83070</t>
+          <t>83748</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2744,12 +2744,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,49%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>259210</t>
+          <t>243140</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>450428</t>
+          <t>446693</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>419551</t>
+          <t>420586</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>540136</t>
+          <t>543253</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>36,98%</t>
+          <t>37,19%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>693752</t>
+          <t>664389</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>978494</t>
+          <t>973570</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,45%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>14167</t>
+          <t>14492</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>37768</t>
+          <t>38075</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>8597</t>
+          <t>7981</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>328623</t>
+          <t>299919</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>30609</t>
+          <t>30644</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>368639</t>
+          <t>385109</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>11,25%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1455224</t>
+          <t>1457141</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1671641</t>
+          <t>1677773</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>74,18%</t>
+          <t>74,28%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>85,21%</t>
+          <t>85,52%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>733245</t>
+          <t>741351</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>940900</t>
+          <t>937684</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>50,2%</t>
+          <t>50,75%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>64,41%</t>
+          <t>64,19%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2264430</t>
+          <t>2261899</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2634305</t>
+          <t>2613729</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>66,16%</t>
+          <t>66,09%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>76,37%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>84786</t>
+          <t>82649</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>155792</t>
+          <t>157981</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>118782</t>
+          <t>120810</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>173177</t>
+          <t>176195</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>215480</t>
+          <t>219318</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>317775</t>
+          <t>315820</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,23%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>9218</t>
+          <t>8927</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>28192</t>
+          <t>28001</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>4426</t>
+          <t>4376</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>16393</t>
+          <t>17835</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>16608</t>
+          <t>16541</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>38577</t>
+          <t>40725</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -3341,12 +3341,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>45412</t>
+          <t>47733</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>97309</t>
+          <t>98229</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3356,12 +3356,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3376,12 +3376,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>40183</t>
+          <t>40576</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>67027</t>
+          <t>67644</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3411,12 +3411,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>95319</t>
+          <t>98949</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>154159</t>
+          <t>156137</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P64D$andando_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P64D$andando_2023-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>19380</t>
+          <t>29128</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11953</t>
+          <t>18347</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30748</t>
+          <t>41650</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>42450</t>
+          <t>41945</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>34136</t>
+          <t>33811</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>52604</t>
+          <t>50096</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>52,77%</t>
+          <t>47,67%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>38,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>65,39%</t>
+          <t>56,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>61830</t>
+          <t>71073</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>48890</t>
+          <t>57340</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>78031</t>
+          <t>85734</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>34,03%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1533</t>
+          <t>8683</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>316</t>
+          <t>2120</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6313</t>
+          <t>24235</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1533</t>
+          <t>8683</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>2158</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7124</t>
+          <t>26268</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>10,43%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>108750</t>
+          <t>121664</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>97527</t>
+          <t>106222</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>116942</t>
+          <t>134085</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>74,21%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>73,83%</t>
+          <t>64,8%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>81,79%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>30429</t>
+          <t>34342</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>21544</t>
+          <t>26467</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>38740</t>
+          <t>43212</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>39,03%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>48,16%</t>
+          <t>49,11%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>139179</t>
+          <t>156006</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>123510</t>
+          <t>138634</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>152505</t>
+          <t>171446</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>65,48%</t>
+          <t>61,92%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>58,11%</t>
+          <t>55,03%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>71,75%</t>
+          <t>68,05%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6072</t>
+          <t>9940</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2691</t>
+          <t>4974</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12271</t>
+          <t>17843</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17033</t>
+          <t>16332</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10294</t>
+          <t>10525</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32330</t>
+          <t>23357</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>23105</t>
+          <t>26272</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13999</t>
+          <t>18159</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>41845</t>
+          <t>37872</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>15,03%</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>2045</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1187,12 +1187,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6229</t>
+          <t>6554</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>2045</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6271</t>
+          <t>7364</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -1290,32 +1290,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3316</t>
+          <t>4402</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>773</t>
+          <t>1107</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9950</t>
+          <t>10898</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1325,32 +1325,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3349</t>
+          <t>4943</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1452</t>
+          <t>2319</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7321</t>
+          <t>9170</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1360,32 +1360,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>6665</t>
+          <t>9345</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3333</t>
+          <t>5039</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>13330</t>
+          <t>16300</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,47%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>248484</t>
+          <t>283901</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>132508</t>
+          <t>250696</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>312683</t>
+          <t>320960</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>311968</t>
+          <t>354963</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>240180</t>
+          <t>325756</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>353554</t>
+          <t>379450</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>40,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>560451</t>
+          <t>638864</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>384732</t>
+          <t>592947</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>647313</t>
+          <t>685539</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>30,94%</t>
         </is>
       </c>
     </row>
@@ -1520,102 +1520,102 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14586</t>
+          <t>19810</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6396</t>
+          <t>11349</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27812</t>
+          <t>34310</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
+          <t>2,7%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>8823</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>4761</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>15706</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>1,66%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>28633</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>19168</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>44478</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>1,29%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>0,87%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
           <t>2,01%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>74195</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>3534</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>280571</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>7,85%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>29,69%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>88780</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>16015</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>349697</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>3,81%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>15,03%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1120997</t>
+          <t>959282</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1050924</t>
+          <t>920546</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1242083</t>
+          <t>994937</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>81,09%</t>
+          <t>75,5%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>76,02%</t>
+          <t>72,45%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>78,31%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>554785</t>
+          <t>568276</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>422234</t>
+          <t>541795</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>613816</t>
+          <t>598629</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>58,71%</t>
+          <t>60,12%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>44,68%</t>
+          <t>57,32%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>64,96%</t>
+          <t>63,33%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1675783</t>
+          <t>1527559</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1530667</t>
+          <t>1483646</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1859802</t>
+          <t>1575191</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>72,0%</t>
+          <t>68,94%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>65,77%</t>
+          <t>66,96%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>79,91%</t>
+          <t>71,09%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>92455</t>
+          <t>116479</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>49529</t>
+          <t>93833</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>121500</t>
+          <t>140856</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>94949</t>
+          <t>115558</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>71880</t>
+          <t>97220</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>118154</t>
+          <t>136374</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>187404</t>
+          <t>232037</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>130426</t>
+          <t>203492</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>222651</t>
+          <t>263852</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>11,91%</t>
         </is>
       </c>
     </row>
@@ -1859,67 +1859,67 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>11095</t>
+          <t>12679</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5081</t>
+          <t>6946</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21558</t>
+          <t>23115</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1,82%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>8615</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>3529</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>17923</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0,91%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
           <t>0,37%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>1,56%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>4790</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>1877</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>10043</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>15885</t>
+          <t>21294</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8471</t>
+          <t>13080</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>26363</t>
+          <t>32897</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -1972,32 +1972,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>28988</t>
+          <t>32894</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13982</t>
+          <t>21696</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>46913</t>
+          <t>47317</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2007,32 +2007,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>25675</t>
+          <t>31825</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>17591</t>
+          <t>22902</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>37144</t>
+          <t>43035</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2042,32 +2042,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>54663</t>
+          <t>64719</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>34662</t>
+          <t>50097</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>74706</t>
+          <t>82836</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,74%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>114896</t>
+          <t>125037</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>95323</t>
+          <t>106185</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>136533</t>
+          <t>145534</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>143510</t>
+          <t>158021</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>128708</t>
+          <t>141328</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>162735</t>
+          <t>177772</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,38%</t>
+          <t>37,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>258406</t>
+          <t>283059</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>234972</t>
+          <t>257663</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>284806</t>
+          <t>313696</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>32,51%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8852</t>
+          <t>10183</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4195</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16126</t>
+          <t>19770</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4984</t>
+          <t>7745</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2404</t>
+          <t>3924</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10286</t>
+          <t>13833</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>13836</t>
+          <t>17928</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>8562</t>
+          <t>10657</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>22011</t>
+          <t>26476</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>299903</t>
+          <t>322279</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>278834</t>
+          <t>297147</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>323532</t>
+          <t>344168</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>67,05%</t>
+          <t>66,1%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>62,34%</t>
+          <t>60,94%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>72,33%</t>
+          <t>70,59%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>294429</t>
+          <t>317276</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>276325</t>
+          <t>298869</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>311402</t>
+          <t>334253</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>67,63%</t>
+          <t>66,45%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>63,47%</t>
+          <t>62,59%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>71,53%</t>
+          <t>70,0%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>594332</t>
+          <t>639555</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>565212</t>
+          <t>607638</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>622478</t>
+          <t>667138</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>67,34%</t>
+          <t>66,27%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>64,04%</t>
+          <t>62,96%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>70,52%</t>
+          <t>69,13%</t>
         </is>
       </c>
     </row>
@@ -2428,17 +2428,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>28465</t>
+          <t>31026</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>18690</t>
+          <t>20992</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>41834</t>
+          <t>45910</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>36661</t>
+          <t>40884</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>27118</t>
+          <t>30903</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>48443</t>
+          <t>52020</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>65126</t>
+          <t>71911</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>51019</t>
+          <t>58607</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>81410</t>
+          <t>90989</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,43%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>4257</t>
+          <t>6715</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1360</t>
+          <t>2653</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10981</t>
+          <t>15059</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,17 +2581,17 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>1372</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10560</t>
+          <t>10933</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>8586</t>
+          <t>11045</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3453</t>
+          <t>5443</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>17628</t>
+          <t>20302</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -2654,32 +2654,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>41082</t>
+          <t>48728</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>28985</t>
+          <t>34448</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>57249</t>
+          <t>64918</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2689,32 +2689,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>23213</t>
+          <t>26060</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>15878</t>
+          <t>17824</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>33010</t>
+          <t>36220</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2724,32 +2724,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>64295</t>
+          <t>74788</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>50803</t>
+          <t>58285</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>83748</t>
+          <t>96101</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,96%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>382759</t>
+          <t>438067</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>243140</t>
+          <t>396492</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>446693</t>
+          <t>480445</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>497928</t>
+          <t>554929</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>420586</t>
+          <t>521134</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>543253</t>
+          <t>589002</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>36,73%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>34,5%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>37,19%</t>
+          <t>38,99%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>880687</t>
+          <t>992996</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>664389</t>
+          <t>938885</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>973570</t>
+          <t>1045746</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>30,46%</t>
         </is>
       </c>
     </row>
@@ -2884,32 +2884,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>24970</t>
+          <t>38677</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>14492</t>
+          <t>25905</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>38075</t>
+          <t>61699</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>79179</t>
+          <t>16568</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>7981</t>
+          <t>10366</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>299919</t>
+          <t>24655</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>104150</t>
+          <t>55245</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>30644</t>
+          <t>39980</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>385109</t>
+          <t>77730</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1529650</t>
+          <t>1403226</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1457141</t>
+          <t>1359288</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1677773</t>
+          <t>1447380</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>77,97%</t>
+          <t>73,01%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>74,28%</t>
+          <t>70,72%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>75,31%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>879643</t>
+          <t>919894</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>741351</t>
+          <t>885682</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>937684</t>
+          <t>956010</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>60,22%</t>
+          <t>60,89%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>50,75%</t>
+          <t>58,63%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>64,19%</t>
+          <t>63,28%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>2409294</t>
+          <t>2323120</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2261899</t>
+          <t>2263791</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2613729</t>
+          <t>2378561</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>70,4%</t>
+          <t>67,67%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>66,09%</t>
+          <t>65,95%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>76,37%</t>
+          <t>69,29%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>126992</t>
+          <t>157445</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>82649</t>
+          <t>131243</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>157981</t>
+          <t>186454</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>148643</t>
+          <t>172774</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>120810</t>
+          <t>152104</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>176195</t>
+          <t>196813</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>275635</t>
+          <t>330220</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>219318</t>
+          <t>297716</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>315820</t>
+          <t>367058</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>10,69%</t>
         </is>
       </c>
     </row>
@@ -3223,67 +3223,67 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>16670</t>
+          <t>21439</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>8927</t>
+          <t>12920</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>28001</t>
+          <t>34186</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
+          <t>0,67%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>1,78%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>12945</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>6992</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>24819</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>0,86%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
           <t>0,46%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>1,43%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>9120</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>4376</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>17835</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>25791</t>
+          <t>34384</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>16541</t>
+          <t>24038</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>40725</t>
+          <t>49860</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -3336,32 +3336,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>73386</t>
+          <t>86023</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>47733</t>
+          <t>66607</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>98229</t>
+          <t>107011</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3371,32 +3371,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>52237</t>
+          <t>62829</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>40576</t>
+          <t>49842</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>67644</t>
+          <t>77526</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3406,32 +3406,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>125623</t>
+          <t>148852</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>98949</t>
+          <t>126935</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>156137</t>
+          <t>177086</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>5,16%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P64D$andando_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P64D$andando_2023-Estudios-trans_orig.xlsx
@@ -941,112 +941,112 @@
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>En vehículo particular</t>
+          <t>No realiza estos trayectos</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>121664</t>
+          <t>4402</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>106222</t>
+          <t>1107</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>134085</t>
+          <t>10898</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>74,21%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>64,8%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>81,79%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>34342</t>
+          <t>4943</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>26467</t>
+          <t>2319</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>43212</t>
+          <t>9170</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>39,03%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>49,11%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>156006</t>
+          <t>9345</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>138634</t>
+          <t>5039</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>171446</t>
+          <t>16300</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>61,92%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>55,03%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>68,05%</t>
+          <t>6,47%</t>
         </is>
       </c>
     </row>
@@ -1054,112 +1054,112 @@
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>En transporte público</t>
+          <t>En otros medios</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9940</t>
+          <t>2045</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4974</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17843</t>
+          <t>6554</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16332</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10525</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23357</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>26272</t>
+          <t>2045</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18159</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>37872</t>
+          <t>7364</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -1167,112 +1167,112 @@
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>En otros medios</t>
+          <t>En vehículo particular</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>109</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2045</t>
+          <t>121664</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>106222</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6554</t>
+          <t>134085</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>74,21%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>64,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>81,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>46</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34342</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>26467</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>43212</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>39,03%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>49,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>155</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2045</t>
+          <t>156006</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>138634</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7364</t>
+          <t>171446</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>61,92%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>55,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>68,05%</t>
         </is>
       </c>
     </row>
@@ -1280,112 +1280,112 @@
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>No realiza estos trayectos</t>
+          <t>En transporte público</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4402</t>
+          <t>9940</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1107</t>
+          <t>4974</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10898</t>
+          <t>17843</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4943</t>
+          <t>16332</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2319</t>
+          <t>10525</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9170</t>
+          <t>23357</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>31</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>9345</t>
+          <t>26272</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>5039</t>
+          <t>18159</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>16300</t>
+          <t>37872</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>15,03%</t>
         </is>
       </c>
     </row>
@@ -1623,112 +1623,112 @@
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>En vehículo particular</t>
+          <t>No realiza estos trayectos</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>835</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>959282</t>
+          <t>32894</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>920546</t>
+          <t>21696</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>994937</t>
+          <t>47317</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>75,5%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>72,45%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>78,31%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>777</t>
+          <t>42</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>568276</t>
+          <t>31825</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>541795</t>
+          <t>22902</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>598629</t>
+          <t>43035</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>60,12%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>57,32%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>63,33%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>1612</t>
+          <t>69</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1527559</t>
+          <t>64719</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1483646</t>
+          <t>50097</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1575191</t>
+          <t>82836</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>68,94%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>66,96%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>71,09%</t>
+          <t>3,74%</t>
         </is>
       </c>
     </row>
@@ -1736,112 +1736,112 @@
       <c r="A13" s="1" t="n"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>En transporte público</t>
+          <t>En otros medios</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>116479</t>
+          <t>12679</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>93833</t>
+          <t>6946</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>140856</t>
+          <t>23115</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>115558</t>
+          <t>8615</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>97220</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>136374</t>
+          <t>17923</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>232037</t>
+          <t>21294</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>203492</t>
+          <t>13080</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>263852</t>
+          <t>32897</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -1849,112 +1849,112 @@
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>En otros medios</t>
+          <t>En vehículo particular</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>835</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>12679</t>
+          <t>959282</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6946</t>
+          <t>920546</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>23115</t>
+          <t>994937</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>75,5%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>72,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>78,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>777</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>8615</t>
+          <t>568276</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>541795</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>17923</t>
+          <t>598629</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>60,12%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>57,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>63,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1612</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>21294</t>
+          <t>1527559</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>13080</t>
+          <t>1483646</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>32897</t>
+          <t>1575191</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>68,94%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>66,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>71,09%</t>
         </is>
       </c>
     </row>
@@ -1962,112 +1962,112 @@
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>No realiza estos trayectos</t>
+          <t>En transporte público</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>94</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>32894</t>
+          <t>116479</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>21696</t>
+          <t>93833</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>47317</t>
+          <t>140856</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>135</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>31825</t>
+          <t>115558</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>22902</t>
+          <t>97220</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>43035</t>
+          <t>136374</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>229</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>64719</t>
+          <t>232037</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>50097</t>
+          <t>203492</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>82836</t>
+          <t>263852</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>11,91%</t>
         </is>
       </c>
     </row>
@@ -2305,112 +2305,112 @@
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>En vehículo particular</t>
+          <t>No realiza estos trayectos</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>37</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>322279</t>
+          <t>48728</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>297147</t>
+          <t>34448</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>344168</t>
+          <t>64918</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>66,1%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>60,94%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>70,59%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>317276</t>
+          <t>26060</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>298869</t>
+          <t>17824</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>334253</t>
+          <t>36220</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>66,45%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>62,59%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>70,0%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>71</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>639555</t>
+          <t>74788</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>607638</t>
+          <t>58285</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>667138</t>
+          <t>96101</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>66,27%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>62,96%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>69,13%</t>
+          <t>9,96%</t>
         </is>
       </c>
     </row>
@@ -2418,112 +2418,112 @@
       <c r="A19" s="1" t="n"/>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>En transporte público</t>
+          <t>En otros medios</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>31026</t>
+          <t>6715</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>20992</t>
+          <t>2653</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>45910</t>
+          <t>15059</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>40884</t>
+          <t>4330</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>30903</t>
+          <t>1372</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>52020</t>
+          <t>10933</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>71911</t>
+          <t>11045</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>58607</t>
+          <t>5443</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>90989</t>
+          <t>20302</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -2531,112 +2531,112 @@
       <c r="A20" s="1" t="n"/>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>En otros medios</t>
+          <t>En vehículo particular</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>287</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>6715</t>
+          <t>322279</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2653</t>
+          <t>297147</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>15059</t>
+          <t>344168</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>66,1%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>60,94%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>70,59%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>433</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>4330</t>
+          <t>317276</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1372</t>
+          <t>298869</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10933</t>
+          <t>334253</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>66,45%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>62,59%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>70,0%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>720</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>11045</t>
+          <t>639555</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5443</t>
+          <t>607638</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>20302</t>
+          <t>667138</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>66,27%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>62,96%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>69,13%</t>
         </is>
       </c>
     </row>
@@ -2644,112 +2644,112 @@
       <c r="A21" s="1" t="n"/>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>No realiza estos trayectos</t>
+          <t>En transporte público</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>48728</t>
+          <t>31026</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>34448</t>
+          <t>20992</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>64918</t>
+          <t>45910</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>52</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>26060</t>
+          <t>40884</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>17824</t>
+          <t>30903</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>36220</t>
+          <t>52020</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>79</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>74788</t>
+          <t>71911</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>58285</t>
+          <t>58607</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>96101</t>
+          <t>90989</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,43%</t>
         </is>
       </c>
     </row>
@@ -2987,112 +2987,112 @@
       <c r="A24" s="1" t="n"/>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>En vehículo particular</t>
+          <t>No realiza estos trayectos</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1231</t>
+          <t>68</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1403226</t>
+          <t>86023</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1359288</t>
+          <t>66607</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1447380</t>
+          <t>107011</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>73,01%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>70,72%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>75,31%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1256</t>
+          <t>84</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>919894</t>
+          <t>62829</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>885682</t>
+          <t>49842</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>956010</t>
+          <t>77526</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>60,89%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>58,63%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>63,28%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>2487</t>
+          <t>152</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>2323120</t>
+          <t>148852</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2263791</t>
+          <t>126935</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2378561</t>
+          <t>177086</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>67,67%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>65,95%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>69,29%</t>
+          <t>5,16%</t>
         </is>
       </c>
     </row>
@@ -3100,112 +3100,112 @@
       <c r="A25" s="1" t="n"/>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>En transporte público</t>
+          <t>En otros medios</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>157445</t>
+          <t>21439</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>131243</t>
+          <t>12920</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>186454</t>
+          <t>34186</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>172774</t>
+          <t>12945</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>152104</t>
+          <t>6992</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>196813</t>
+          <t>24819</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>31</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>330220</t>
+          <t>34384</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>297716</t>
+          <t>24038</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>367058</t>
+          <t>49860</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -3213,112 +3213,112 @@
       <c r="A26" s="1" t="n"/>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>En otros medios</t>
+          <t>En vehículo particular</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>1231</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>21439</t>
+          <t>1403226</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>12920</t>
+          <t>1359288</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>34186</t>
+          <t>1447380</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>73,01%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>70,72%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>75,31%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1256</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>12945</t>
+          <t>919894</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>6992</t>
+          <t>885682</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>24819</t>
+          <t>956010</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>60,89%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>58,63%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>63,28%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>2487</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>34384</t>
+          <t>2323120</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>24038</t>
+          <t>2263791</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>49860</t>
+          <t>2378561</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>67,67%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>65,95%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>69,29%</t>
         </is>
       </c>
     </row>
@@ -3326,112 +3326,112 @@
       <c r="A27" s="1" t="n"/>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>No realiza estos trayectos</t>
+          <t>En transporte público</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>131</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>86023</t>
+          <t>157445</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>66607</t>
+          <t>131243</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>107011</t>
+          <t>186454</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>208</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>62829</t>
+          <t>172774</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>49842</t>
+          <t>152104</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>77526</t>
+          <t>196813</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>339</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>148852</t>
+          <t>330220</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>126935</t>
+          <t>297716</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>177086</t>
+          <t>367058</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>10,69%</t>
         </is>
       </c>
     </row>
